--- a/A_2018/chrVII:347117-396704_254_finemapping.xlsx
+++ b/A_2018/chrVII:347117-396704_254_finemapping.xlsx
@@ -1100,13 +1100,13 @@
     <t xml:space="preserve">Biosynthesis of secondary metabolites - Saccharomyces cerevisiae (budding yeast)</t>
   </si>
   <si>
-    <t xml:space="preserve">32/112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">301/1898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YBR176W/YBR213W/YCL030C/YDL193W/YDL182W/YDR158W/YDR232W/YDR487C/YER005W/YER069W/YER099C/YHR072W/YHR123W/YHR190W/YHR208W/YIL145C/YIL094C/YJL167W/YJR019C/YLR058C/YLR142W/YLR153C/YLR209C/YML126C/YMR165C/YMR208W/YNR041C/YNR043W/YOR184W/YPL117C/YPL028W/YPR006C</t>
+    <t xml:space="preserve">33/112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">309/1898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YBR176W/YBR213W/YCL030C/YDL193W/YDL182W/YDR158W/YDR232W/YDR487C/YER005W/YER069W/YER099C/YHR072W/YHR123W/YHR190W/YHR208W/YIL145C/YIL094C/YJL167W/YJR019C/YLR058C/YLR142W/YLR153C/YLR209C/YML126C/YMR165C/YMR208W/YNR041C/YNR043W/YOR184W/YPL117C/YPL028W/YPR006C/YPR069C</t>
   </si>
   <si>
     <t xml:space="preserve">sce01240</t>
@@ -36706,19 +36706,19 @@
         <v>359</v>
       </c>
       <c r="G4" t="n">
-        <v>0.000315531785504397</v>
+        <v>0.000223460717688102</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00725723106660114</v>
+        <v>0.00513959650682635</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00642134861728247</v>
+        <v>0.00454762162312629</v>
       </c>
       <c r="J4" t="s">
         <v>360</v>
       </c>
       <c r="K4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
